--- a/src/results_template/CEC2022/10Dim.xlsx
+++ b/src/results_template/CEC2022/10Dim.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\Research\Project Test\Base-Optimization-Framework\src\results_template\CEC2022\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\WorkSpace\Research\Project Test\src\results_template\CEC2022\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{85499F44-3051-4C3F-A4BF-A7FBDCADF95A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BCF5704-60DB-4B10-8D90-0EE2794B5C2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Conclusions" sheetId="1" r:id="rId1"/>
@@ -22,20 +22,8 @@
     <sheet name="Friedman" sheetId="7" r:id="rId7"/>
     <sheet name="Explanation" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
+  <calcPr calcId="0"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -44,12 +32,57 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="103">
   <si>
     <t>Comparison of optimization results for the CEC benchmark functions 2022 (10 Dim)</t>
   </si>
   <si>
     <t>Functions</t>
+  </si>
+  <si>
+    <t>Algorithm 1</t>
+  </si>
+  <si>
+    <t>Algorithm 2</t>
+  </si>
+  <si>
+    <t>Algorithm 3</t>
+  </si>
+  <si>
+    <t>Algorithm 4</t>
+  </si>
+  <si>
+    <t>Algorithm 5</t>
+  </si>
+  <si>
+    <t>Algorithm 6</t>
+  </si>
+  <si>
+    <t>Algorithm 7</t>
+  </si>
+  <si>
+    <t>Algorithm 8</t>
+  </si>
+  <si>
+    <t>Algorithm 9</t>
+  </si>
+  <si>
+    <t>Algorithm 10</t>
+  </si>
+  <si>
+    <t>Algorithm 11</t>
+  </si>
+  <si>
+    <t>Algorithm 12</t>
+  </si>
+  <si>
+    <t>Algorithm 13</t>
+  </si>
+  <si>
+    <t>Algorithm 14</t>
+  </si>
+  <si>
+    <t>Algorithm 15</t>
   </si>
   <si>
     <t>Unimodal
@@ -113,177 +146,129 @@
     <t>F12</t>
   </si>
   <si>
-    <t>Algorithm 1</t>
-  </si>
-  <si>
-    <t>Algorithm 2</t>
-  </si>
-  <si>
-    <t>Algorithm 3</t>
-  </si>
-  <si>
-    <t>Algorithm 4</t>
-  </si>
-  <si>
-    <t>Algorithm 5</t>
-  </si>
-  <si>
-    <t>Algorithm 6</t>
-  </si>
-  <si>
-    <t>Algorithm 7</t>
-  </si>
-  <si>
-    <t>Algorithm 8</t>
-  </si>
-  <si>
-    <t>Algorithm 9</t>
-  </si>
-  <si>
-    <t>Algorithm 10</t>
-  </si>
-  <si>
-    <t>Algorithm 11</t>
-  </si>
-  <si>
-    <t>Algorithm 12</t>
-  </si>
-  <si>
-    <t>Algorithm 13</t>
-  </si>
-  <si>
-    <t>Algorithm 14</t>
-  </si>
-  <si>
-    <t>Algorithm 15</t>
-  </si>
-  <si>
-    <t>Number of Best Functions</t>
+    <t>P-value of the one-sided Welch t-test for the CEC benchmark functions 2022 (10 Dim)</t>
+  </si>
+  <si>
+    <t>Function</t>
+  </si>
+  <si>
+    <t>alg_base vs alg2</t>
+  </si>
+  <si>
+    <t>alg_base vs alg3</t>
+  </si>
+  <si>
+    <t>alg_base vs alg4</t>
+  </si>
+  <si>
+    <t>alg_base vs alg5</t>
+  </si>
+  <si>
+    <t>alg_base vs alg6</t>
+  </si>
+  <si>
+    <t>alg_base vs alg7</t>
+  </si>
+  <si>
+    <t>alg_base vs alg8</t>
+  </si>
+  <si>
+    <t>alg_base vs alg9</t>
+  </si>
+  <si>
+    <t>alg_base vs alg10</t>
+  </si>
+  <si>
+    <t>alg_base vs alg11</t>
+  </si>
+  <si>
+    <t>alg_base vs alg12</t>
+  </si>
+  <si>
+    <t>alg_base vs alg13</t>
+  </si>
+  <si>
+    <t>alg_base vs alg14</t>
+  </si>
+  <si>
+    <t>alg_base vs alg15</t>
+  </si>
+  <si>
+    <t>Decision (h) of the one-sided Welch t-test for the CEC benchmark functions 2022 (10 Dim)</t>
+  </si>
+  <si>
+    <t>P-value of the one-sided Wilcoxon rank-sum test for the CEC benchmark functions 2022 (10 Dim)</t>
+  </si>
+  <si>
+    <t>Decision (h) of the one-sided Wilcoxon rank-sum test for the CEC benchmark functions 2022 (10 Dim)</t>
+  </si>
+  <si>
+    <t>Rank-sum statistic (W) for the Wilcoxon rank-sum test for the CEC benchmark functions 2022 (10 Dim)</t>
+  </si>
+  <si>
+    <t>Function ranking and overall Friedman analysis for the CEC benchmark functions 2022 (10 Dim)</t>
+  </si>
+  <si>
+    <t>Algorithm 1 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 2 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 3 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 4 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 5 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 6 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 7 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 8 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 9 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 10 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 11 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 12 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 13 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 14 Rank</t>
+  </si>
+  <si>
+    <t>Algorithm 15 Rank</t>
+  </si>
+  <si>
+    <t>Best Algorithm</t>
+  </si>
+  <si>
+    <t>Kruskal-Wallis p</t>
+  </si>
+  <si>
+    <t>Significant?</t>
+  </si>
+  <si>
+    <t>Average Rank</t>
   </si>
   <si>
     <t>Overall Rank</t>
   </si>
   <si>
-    <t>P-value of the one-sided Welch t-test for the CEC benchmark functions 2022 (10 Dim)</t>
-  </si>
-  <si>
-    <t>Function</t>
-  </si>
-  <si>
-    <t>alg_base vs alg2</t>
-  </si>
-  <si>
-    <t>alg_base vs alg3</t>
-  </si>
-  <si>
-    <t>alg_base vs alg4</t>
-  </si>
-  <si>
-    <t>alg_base vs alg5</t>
-  </si>
-  <si>
-    <t>alg_base vs alg6</t>
-  </si>
-  <si>
-    <t>alg_base vs alg7</t>
-  </si>
-  <si>
-    <t>alg_base vs alg8</t>
-  </si>
-  <si>
-    <t>alg_base vs alg9</t>
-  </si>
-  <si>
-    <t>alg_base vs alg10</t>
-  </si>
-  <si>
-    <t>alg_base vs alg11</t>
-  </si>
-  <si>
-    <t>alg_base vs alg12</t>
-  </si>
-  <si>
-    <t>alg_base vs alg13</t>
-  </si>
-  <si>
-    <t>alg_base vs alg14</t>
-  </si>
-  <si>
-    <t>alg_base vs alg15</t>
-  </si>
-  <si>
-    <t>Decision (h) of the one-sided Welch t-test for the CEC benchmark functions 2022 (10 Dim)</t>
-  </si>
-  <si>
-    <t>P-value of the one-sided Wilcoxon rank-sum test for the CEC benchmark functions 2022 (10 Dim)</t>
-  </si>
-  <si>
-    <t>Decision (h) of the one-sided Wilcoxon rank-sum test for the CEC benchmark functions 2022 (10 Dim)</t>
-  </si>
-  <si>
-    <t>Rank-sum statistic (W) for the Wilcoxon rank-sum test for the CEC benchmark functions 2022 (10 Dim)</t>
-  </si>
-  <si>
-    <t>Function ranking and overall Friedman analysis for the CEC benchmark functions 2022 (10 Dim)</t>
-  </si>
-  <si>
-    <t>Algorithm 1 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 2 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 3 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 4 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 5 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 6 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 7 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 8 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 9 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 10 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 11 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 12 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 13 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 14 Rank</t>
-  </si>
-  <si>
-    <t>Algorithm 15 Rank</t>
-  </si>
-  <si>
-    <t>Best Algorithm</t>
-  </si>
-  <si>
-    <t>Kruskal-Wallis p</t>
-  </si>
-  <si>
-    <t>Significant?</t>
-  </si>
-  <si>
-    <t>Average Rank</t>
-  </si>
-  <si>
     <t>Overall Friedman Test</t>
   </si>
   <si>
@@ -354,6 +339,12 @@
   </si>
   <si>
     <t>Optional figures showing the distribution of final objective values across independent runs for each function and algorithm.</t>
+  </si>
+  <si>
+    <t>Total number of best answers</t>
+  </si>
+  <si>
+    <t>Total number of equal-best answers</t>
   </si>
 </sst>
 </file>
@@ -490,7 +481,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -550,7 +541,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -566,23 +556,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -590,14 +565,36 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -756,9 +753,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -863,99 +860,99 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R40"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.109375" style="7" customWidth="1"/>
+    <col min="1" max="1" width="11.140625" style="7" customWidth="1"/>
     <col min="2" max="2" width="4" style="7" customWidth="1"/>
     <col min="3" max="3" width="6" style="7" customWidth="1"/>
-    <col min="4" max="12" width="10.109375" style="7" customWidth="1"/>
-    <col min="13" max="18" width="11.109375" style="7" customWidth="1"/>
-    <col min="19" max="16384" width="8.88671875" style="7"/>
+    <col min="4" max="12" width="11.28515625" style="7" customWidth="1"/>
+    <col min="13" max="18" width="12.28515625" style="7" customWidth="1"/>
+    <col min="19" max="16384" width="8.85546875" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="29" t="s">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29"/>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="29"/>
-      <c r="I1" s="29"/>
-      <c r="J1" s="29"/>
-      <c r="K1" s="29"/>
-      <c r="L1" s="29"/>
-      <c r="M1" s="29"/>
-      <c r="N1" s="29"/>
-      <c r="O1" s="29"/>
-      <c r="P1" s="29"/>
-      <c r="Q1" s="29"/>
-      <c r="R1" s="29"/>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
+      <c r="M1" s="34"/>
+      <c r="N1" s="34"/>
+      <c r="O1" s="34"/>
+      <c r="P1" s="34"/>
+      <c r="Q1" s="34"/>
+      <c r="R1" s="34"/>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="11"/>
       <c r="C2" s="11"/>
       <c r="D2" s="11" t="s">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="H2" s="11" t="s">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="I2" s="11" t="s">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="J2" s="11" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="L2" s="11" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="M2" s="11" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="N2" s="11" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="O2" s="11" t="s">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="P2" s="11" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="Q2" s="11" t="s">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="R2" s="11" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>3</v>
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>18</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="4"/>
@@ -973,13 +970,11 @@
       <c r="Q3" s="4"/>
       <c r="R3" s="4"/>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A4" s="30"/>
-      <c r="B4" s="9" t="s">
-        <v>3</v>
-      </c>
+    <row r="4" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="33"/>
+      <c r="B4" s="31"/>
       <c r="C4" s="9" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
@@ -997,13 +992,11 @@
       <c r="Q4" s="8"/>
       <c r="R4" s="8"/>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A5" s="31"/>
-      <c r="B5" s="5" t="s">
-        <v>3</v>
-      </c>
+    <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="36"/>
+      <c r="B5" s="32"/>
       <c r="C5" s="5" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
@@ -1021,15 +1014,15 @@
       <c r="Q5" s="6"/>
       <c r="R5" s="6"/>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A6" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>8</v>
+    <row r="6" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>23</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D6" s="4"/>
       <c r="E6" s="4"/>
@@ -1047,13 +1040,11 @@
       <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A7" s="30"/>
-      <c r="B7" s="9" t="s">
-        <v>8</v>
-      </c>
+    <row r="7" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="33"/>
+      <c r="B7" s="31"/>
       <c r="C7" s="9" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D7" s="8"/>
       <c r="E7" s="8"/>
@@ -1071,13 +1062,11 @@
       <c r="Q7" s="8"/>
       <c r="R7" s="8"/>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A8" s="30"/>
-      <c r="B8" s="5" t="s">
-        <v>8</v>
-      </c>
+    <row r="8" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="33"/>
+      <c r="B8" s="32"/>
       <c r="C8" s="5" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
@@ -1095,13 +1084,13 @@
       <c r="Q8" s="6"/>
       <c r="R8" s="6"/>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A9" s="30"/>
-      <c r="B9" s="3" t="s">
-        <v>9</v>
+    <row r="9" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="33"/>
+      <c r="B9" s="30" t="s">
+        <v>24</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -1119,13 +1108,11 @@
       <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A10" s="30"/>
-      <c r="B10" s="9" t="s">
-        <v>9</v>
-      </c>
+    <row r="10" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="33"/>
+      <c r="B10" s="31"/>
       <c r="C10" s="9" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D10" s="8"/>
       <c r="E10" s="8"/>
@@ -1143,13 +1130,11 @@
       <c r="Q10" s="8"/>
       <c r="R10" s="8"/>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A11" s="30"/>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
+    <row r="11" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="33"/>
+      <c r="B11" s="32"/>
       <c r="C11" s="5" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D11" s="6"/>
       <c r="E11" s="6"/>
@@ -1167,13 +1152,13 @@
       <c r="Q11" s="6"/>
       <c r="R11" s="6"/>
     </row>
-    <row r="12" spans="1:18" ht="11.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="30"/>
-      <c r="B12" s="3" t="s">
-        <v>10</v>
+    <row r="12" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="33"/>
+      <c r="B12" s="30" t="s">
+        <v>25</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D12" s="4"/>
       <c r="E12" s="4"/>
@@ -1191,13 +1176,11 @@
       <c r="Q12" s="4"/>
       <c r="R12" s="4"/>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A13" s="30"/>
-      <c r="B13" s="9" t="s">
-        <v>10</v>
-      </c>
+    <row r="13" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="33"/>
+      <c r="B13" s="31"/>
       <c r="C13" s="9" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D13" s="8"/>
       <c r="E13" s="8"/>
@@ -1215,13 +1198,11 @@
       <c r="Q13" s="8"/>
       <c r="R13" s="8"/>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="30"/>
-      <c r="B14" s="5" t="s">
-        <v>10</v>
-      </c>
+    <row r="14" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="33"/>
+      <c r="B14" s="32"/>
       <c r="C14" s="5" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
@@ -1239,13 +1220,13 @@
       <c r="Q14" s="6"/>
       <c r="R14" s="6"/>
     </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A15" s="30"/>
-      <c r="B15" s="3" t="s">
-        <v>11</v>
+    <row r="15" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="33"/>
+      <c r="B15" s="30" t="s">
+        <v>26</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
@@ -1263,13 +1244,11 @@
       <c r="Q15" s="4"/>
       <c r="R15" s="4"/>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A16" s="30"/>
-      <c r="B16" s="9" t="s">
-        <v>11</v>
-      </c>
+    <row r="16" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="33"/>
+      <c r="B16" s="31"/>
       <c r="C16" s="9" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D16" s="8"/>
       <c r="E16" s="8"/>
@@ -1287,13 +1266,11 @@
       <c r="Q16" s="8"/>
       <c r="R16" s="8"/>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A17" s="31"/>
-      <c r="B17" s="5" t="s">
-        <v>11</v>
-      </c>
+    <row r="17" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="36"/>
+      <c r="B17" s="32"/>
       <c r="C17" s="5" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -1311,15 +1288,15 @@
       <c r="Q17" s="6"/>
       <c r="R17" s="6"/>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A18" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>13</v>
+    <row r="18" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="35" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="30" t="s">
+        <v>28</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -1337,13 +1314,11 @@
       <c r="Q18" s="4"/>
       <c r="R18" s="4"/>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A19" s="30"/>
-      <c r="B19" s="9" t="s">
-        <v>13</v>
-      </c>
+    <row r="19" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="33"/>
+      <c r="B19" s="31"/>
       <c r="C19" s="9" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
@@ -1361,13 +1336,11 @@
       <c r="Q19" s="8"/>
       <c r="R19" s="8"/>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A20" s="30"/>
-      <c r="B20" s="5" t="s">
-        <v>13</v>
-      </c>
+    <row r="20" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="33"/>
+      <c r="B20" s="32"/>
       <c r="C20" s="5" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
@@ -1385,13 +1358,13 @@
       <c r="Q20" s="6"/>
       <c r="R20" s="6"/>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A21" s="30"/>
-      <c r="B21" s="3" t="s">
-        <v>14</v>
+    <row r="21" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="33"/>
+      <c r="B21" s="30" t="s">
+        <v>29</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
@@ -1409,13 +1382,11 @@
       <c r="Q21" s="4"/>
       <c r="R21" s="4"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A22" s="30"/>
-      <c r="B22" s="9" t="s">
-        <v>14</v>
-      </c>
+    <row r="22" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="33"/>
+      <c r="B22" s="31"/>
       <c r="C22" s="9" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D22" s="8"/>
       <c r="E22" s="8"/>
@@ -1433,13 +1404,11 @@
       <c r="Q22" s="8"/>
       <c r="R22" s="8"/>
     </row>
-    <row r="23" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A23" s="30"/>
-      <c r="B23" s="5" t="s">
-        <v>14</v>
-      </c>
+    <row r="23" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="33"/>
+      <c r="B23" s="32"/>
       <c r="C23" s="5" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
@@ -1457,13 +1426,13 @@
       <c r="Q23" s="6"/>
       <c r="R23" s="6"/>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A24" s="30"/>
-      <c r="B24" s="3" t="s">
-        <v>15</v>
+    <row r="24" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="33"/>
+      <c r="B24" s="30" t="s">
+        <v>30</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
@@ -1481,13 +1450,11 @@
       <c r="Q24" s="4"/>
       <c r="R24" s="4"/>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A25" s="30"/>
-      <c r="B25" s="9" t="s">
-        <v>15</v>
-      </c>
+    <row r="25" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="33"/>
+      <c r="B25" s="31"/>
       <c r="C25" s="9" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D25" s="8"/>
       <c r="E25" s="8"/>
@@ -1505,13 +1472,11 @@
       <c r="Q25" s="8"/>
       <c r="R25" s="8"/>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A26" s="31"/>
-      <c r="B26" s="5" t="s">
-        <v>15</v>
-      </c>
+    <row r="26" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="36"/>
+      <c r="B26" s="32"/>
       <c r="C26" s="5" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
@@ -1529,15 +1494,15 @@
       <c r="Q26" s="6"/>
       <c r="R26" s="6"/>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A27" s="32" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>17</v>
+    <row r="27" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="35" t="s">
+        <v>31</v>
+      </c>
+      <c r="B27" s="30" t="s">
+        <v>32</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
@@ -1555,13 +1520,11 @@
       <c r="Q27" s="4"/>
       <c r="R27" s="4"/>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A28" s="30"/>
-      <c r="B28" s="9" t="s">
-        <v>17</v>
-      </c>
+    <row r="28" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="33"/>
+      <c r="B28" s="31"/>
       <c r="C28" s="9" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D28" s="8"/>
       <c r="E28" s="8"/>
@@ -1579,13 +1542,11 @@
       <c r="Q28" s="8"/>
       <c r="R28" s="8"/>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A29" s="30"/>
-      <c r="B29" s="5" t="s">
-        <v>17</v>
-      </c>
+    <row r="29" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="33"/>
+      <c r="B29" s="32"/>
       <c r="C29" s="5" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
@@ -1603,13 +1564,13 @@
       <c r="Q29" s="6"/>
       <c r="R29" s="6"/>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A30" s="30"/>
-      <c r="B30" s="3" t="s">
-        <v>18</v>
+    <row r="30" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="33"/>
+      <c r="B30" s="30" t="s">
+        <v>33</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
@@ -1627,13 +1588,11 @@
       <c r="Q30" s="4"/>
       <c r="R30" s="4"/>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A31" s="30"/>
-      <c r="B31" s="9" t="s">
-        <v>18</v>
-      </c>
+    <row r="31" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="33"/>
+      <c r="B31" s="31"/>
       <c r="C31" s="9" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D31" s="8"/>
       <c r="E31" s="8"/>
@@ -1651,13 +1610,11 @@
       <c r="Q31" s="8"/>
       <c r="R31" s="8"/>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A32" s="30"/>
-      <c r="B32" s="5" t="s">
-        <v>18</v>
-      </c>
+    <row r="32" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="33"/>
+      <c r="B32" s="32"/>
       <c r="C32" s="5" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D32" s="6"/>
       <c r="E32" s="6"/>
@@ -1675,13 +1632,13 @@
       <c r="Q32" s="6"/>
       <c r="R32" s="6"/>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A33" s="30"/>
-      <c r="B33" s="3" t="s">
+    <row r="33" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="33"/>
+      <c r="B33" s="30" t="s">
+        <v>34</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>4</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
@@ -1699,13 +1656,11 @@
       <c r="Q33" s="4"/>
       <c r="R33" s="4"/>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A34" s="30"/>
-      <c r="B34" s="9" t="s">
-        <v>19</v>
-      </c>
+    <row r="34" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="33"/>
+      <c r="B34" s="31"/>
       <c r="C34" s="9" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
@@ -1723,13 +1678,11 @@
       <c r="Q34" s="8"/>
       <c r="R34" s="8"/>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A35" s="30"/>
-      <c r="B35" s="5" t="s">
-        <v>19</v>
-      </c>
+    <row r="35" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="33"/>
+      <c r="B35" s="32"/>
       <c r="C35" s="5" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
@@ -1747,13 +1700,13 @@
       <c r="Q35" s="6"/>
       <c r="R35" s="6"/>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A36" s="30"/>
-      <c r="B36" s="3" t="s">
-        <v>20</v>
+    <row r="36" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="33"/>
+      <c r="B36" s="30" t="s">
+        <v>35</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -1771,13 +1724,11 @@
       <c r="Q36" s="4"/>
       <c r="R36" s="4"/>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A37" s="30"/>
-      <c r="B37" s="9" t="s">
+    <row r="37" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="33"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="C37" s="9" t="s">
-        <v>5</v>
       </c>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
@@ -1795,13 +1746,11 @@
       <c r="Q37" s="8"/>
       <c r="R37" s="8"/>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A38" s="31"/>
-      <c r="B38" s="5" t="s">
-        <v>20</v>
-      </c>
+    <row r="38" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="36"/>
+      <c r="B38" s="32"/>
       <c r="C38" s="5" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
@@ -1819,59 +1768,71 @@
       <c r="Q38" s="6"/>
       <c r="R38" s="6"/>
     </row>
-    <row r="39" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="B39" s="35"/>
-      <c r="C39" s="35"/>
-      <c r="D39" s="36"/>
-      <c r="E39" s="36"/>
-      <c r="F39" s="36"/>
-      <c r="G39" s="36"/>
-      <c r="H39" s="36"/>
-      <c r="I39" s="36"/>
-      <c r="J39" s="36"/>
-      <c r="K39" s="36"/>
-      <c r="L39" s="36"/>
-      <c r="M39" s="36"/>
-      <c r="N39" s="36"/>
-      <c r="O39" s="36"/>
-      <c r="P39" s="36"/>
-      <c r="Q39" s="36"/>
-      <c r="R39" s="36"/>
-    </row>
-    <row r="40" spans="1:18" ht="25.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="38"/>
-      <c r="C40" s="38"/>
-      <c r="D40" s="39"/>
-      <c r="E40" s="39"/>
-      <c r="F40" s="39"/>
-      <c r="G40" s="39"/>
-      <c r="H40" s="39"/>
-      <c r="I40" s="39"/>
-      <c r="J40" s="39"/>
-      <c r="K40" s="39"/>
-      <c r="L40" s="39"/>
-      <c r="M40" s="39"/>
-      <c r="N40" s="39"/>
-      <c r="O40" s="39"/>
-      <c r="P40" s="39"/>
-      <c r="Q40" s="39"/>
-      <c r="R40" s="39"/>
+    <row r="39" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="38" t="s">
+        <v>101</v>
+      </c>
+      <c r="B39" s="38"/>
+      <c r="C39" s="38"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="29"/>
+      <c r="L39" s="29"/>
+      <c r="M39" s="29"/>
+      <c r="N39" s="29"/>
+      <c r="O39" s="29"/>
+      <c r="P39" s="29"/>
+      <c r="Q39" s="29"/>
+      <c r="R39" s="29"/>
+    </row>
+    <row r="40" spans="1:18" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="B40" s="39"/>
+      <c r="C40" s="39"/>
+      <c r="D40" s="28"/>
+      <c r="E40" s="28"/>
+      <c r="F40" s="28"/>
+      <c r="G40" s="28"/>
+      <c r="H40" s="28"/>
+      <c r="I40" s="28"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
+      <c r="N40" s="28"/>
+      <c r="O40" s="28"/>
+      <c r="P40" s="28"/>
+      <c r="Q40" s="28"/>
+      <c r="R40" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A1:R1"/>
-    <mergeCell ref="A40:C40"/>
+  <mergeCells count="19">
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="A3:A5"/>
     <mergeCell ref="A6:A17"/>
     <mergeCell ref="A18:A26"/>
     <mergeCell ref="A27:A38"/>
+    <mergeCell ref="B3:B5"/>
+    <mergeCell ref="B6:B8"/>
+    <mergeCell ref="B9:B11"/>
+    <mergeCell ref="B12:B14"/>
+    <mergeCell ref="B15:B17"/>
+    <mergeCell ref="B18:B20"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="B33:B35"/>
+    <mergeCell ref="B36:B38"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A1:R1"/>
   </mergeCells>
   <conditionalFormatting sqref="D3:R3">
     <cfRule type="top10" dxfId="15" priority="13" bottom="1" rank="1"/>
@@ -1916,85 +1877,85 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:P14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="2" max="9" width="15.109375" customWidth="1"/>
-    <col min="10" max="15" width="16.109375" customWidth="1"/>
-    <col min="16" max="16" width="8.109375" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="9" width="15.140625" customWidth="1"/>
+    <col min="10" max="15" width="16.140625" customWidth="1"/>
+    <col min="16" max="16" width="8.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="C2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="D2" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="E2" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="F2" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="G2" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="H2" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="I2" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="J2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="K2" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="L2" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="M2" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="N2" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="O2" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N2" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>53</v>
-      </c>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2012,9 +1973,9 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -2032,9 +1993,9 @@
       <c r="O4" s="8"/>
       <c r="P4" s="8"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -2052,9 +2013,9 @@
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2072,9 +2033,9 @@
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -2092,9 +2053,9 @@
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -2112,9 +2073,9 @@
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2132,9 +2093,9 @@
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -2152,9 +2113,9 @@
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -2172,9 +2133,9 @@
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -2192,9 +2153,9 @@
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -2212,9 +2173,9 @@
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -2248,84 +2209,84 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:P14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="2" max="9" width="15.109375" customWidth="1"/>
-    <col min="10" max="15" width="16.109375" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="9" width="15.140625" customWidth="1"/>
+    <col min="10" max="15" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="D2" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="E2" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="F2" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="G2" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="H2" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="I2" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="J2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="K2" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="L2" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="M2" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="N2" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="O2" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N2" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>53</v>
-      </c>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -2343,9 +2304,9 @@
       <c r="O3" s="17"/>
       <c r="P3" s="17"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -2363,9 +2324,9 @@
       <c r="O4" s="18"/>
       <c r="P4" s="18"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
@@ -2383,9 +2344,9 @@
       <c r="O5" s="18"/>
       <c r="P5" s="18"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -2403,9 +2364,9 @@
       <c r="O6" s="18"/>
       <c r="P6" s="18"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
@@ -2423,9 +2384,9 @@
       <c r="O7" s="18"/>
       <c r="P7" s="18"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
@@ -2443,9 +2404,9 @@
       <c r="O8" s="18"/>
       <c r="P8" s="18"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
@@ -2463,9 +2424,9 @@
       <c r="O9" s="18"/>
       <c r="P9" s="18"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
@@ -2483,9 +2444,9 @@
       <c r="O10" s="18"/>
       <c r="P10" s="18"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
@@ -2503,9 +2464,9 @@
       <c r="O11" s="18"/>
       <c r="P11" s="18"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -2523,9 +2484,9 @@
       <c r="O12" s="18"/>
       <c r="P12" s="18"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
@@ -2543,9 +2504,9 @@
       <c r="O13" s="18"/>
       <c r="P13" s="18"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
@@ -2579,84 +2540,84 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:P14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="2" max="9" width="15.109375" customWidth="1"/>
-    <col min="10" max="15" width="16.109375" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="9" width="15.140625" customWidth="1"/>
+    <col min="10" max="15" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="D2" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="E2" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="F2" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="G2" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="H2" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="I2" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="J2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="K2" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="L2" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="M2" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="N2" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="O2" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N2" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>53</v>
-      </c>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -2674,9 +2635,9 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B4" s="8"/>
       <c r="C4" s="8"/>
@@ -2694,9 +2655,9 @@
       <c r="O4" s="8"/>
       <c r="P4" s="8"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -2714,9 +2675,9 @@
       <c r="O5" s="8"/>
       <c r="P5" s="8"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -2734,9 +2695,9 @@
       <c r="O6" s="8"/>
       <c r="P6" s="8"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -2754,9 +2715,9 @@
       <c r="O7" s="8"/>
       <c r="P7" s="8"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B8" s="8"/>
       <c r="C8" s="8"/>
@@ -2774,9 +2735,9 @@
       <c r="O8" s="8"/>
       <c r="P8" s="8"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B9" s="8"/>
       <c r="C9" s="8"/>
@@ -2794,9 +2755,9 @@
       <c r="O9" s="8"/>
       <c r="P9" s="8"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B10" s="8"/>
       <c r="C10" s="8"/>
@@ -2814,9 +2775,9 @@
       <c r="O10" s="8"/>
       <c r="P10" s="8"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B11" s="8"/>
       <c r="C11" s="8"/>
@@ -2834,9 +2795,9 @@
       <c r="O11" s="8"/>
       <c r="P11" s="8"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B12" s="8"/>
       <c r="C12" s="8"/>
@@ -2854,9 +2815,9 @@
       <c r="O12" s="8"/>
       <c r="P12" s="8"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
@@ -2874,9 +2835,9 @@
       <c r="O13" s="8"/>
       <c r="P13" s="8"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
@@ -2910,84 +2871,84 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:P14"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" customWidth="1"/>
-    <col min="2" max="9" width="15.109375" customWidth="1"/>
-    <col min="10" max="15" width="16.109375" customWidth="1"/>
+    <col min="1" max="1" width="8.7109375" customWidth="1"/>
+    <col min="2" max="9" width="15.140625" customWidth="1"/>
+    <col min="10" max="15" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="D2" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="E2" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="F2" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="G2" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="H2" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="I2" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="J2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="K2" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="L2" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="M2" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="N2" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="O2" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N2" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>53</v>
-      </c>
       <c r="P2" s="1"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="17"/>
       <c r="C3" s="17"/>
@@ -3005,9 +2966,9 @@
       <c r="O3" s="17"/>
       <c r="P3" s="17"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -3025,9 +2986,9 @@
       <c r="O4" s="18"/>
       <c r="P4" s="18"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B5" s="18"/>
       <c r="C5" s="18"/>
@@ -3045,9 +3006,9 @@
       <c r="O5" s="18"/>
       <c r="P5" s="18"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -3065,9 +3026,9 @@
       <c r="O6" s="18"/>
       <c r="P6" s="18"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
@@ -3085,9 +3046,9 @@
       <c r="O7" s="18"/>
       <c r="P7" s="18"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
@@ -3105,9 +3066,9 @@
       <c r="O8" s="18"/>
       <c r="P8" s="18"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
@@ -3125,9 +3086,9 @@
       <c r="O9" s="18"/>
       <c r="P9" s="18"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
@@ -3145,9 +3106,9 @@
       <c r="O10" s="18"/>
       <c r="P10" s="18"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
@@ -3165,9 +3126,9 @@
       <c r="O11" s="18"/>
       <c r="P11" s="18"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -3185,9 +3146,9 @@
       <c r="O12" s="18"/>
       <c r="P12" s="18"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="9" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
@@ -3205,9 +3166,9 @@
       <c r="O13" s="18"/>
       <c r="P13" s="18"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
@@ -3241,85 +3202,85 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:P14"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.6640625" style="12" customWidth="1"/>
-    <col min="2" max="9" width="15.109375" style="12" customWidth="1"/>
-    <col min="10" max="15" width="16.109375" style="12" customWidth="1"/>
-    <col min="16" max="16384" width="8.88671875" style="12"/>
+    <col min="1" max="1" width="8.7109375" style="12" customWidth="1"/>
+    <col min="2" max="9" width="15.140625" style="12" customWidth="1"/>
+    <col min="10" max="15" width="16.140625" style="12" customWidth="1"/>
+    <col min="16" max="16384" width="8.85546875" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
-      <c r="K1" s="33"/>
-      <c r="L1" s="33"/>
-      <c r="M1" s="33"/>
-      <c r="N1" s="33"/>
-      <c r="O1" s="33"/>
-      <c r="P1" s="33"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A1" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="37"/>
+      <c r="C1" s="37"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
+      <c r="M1" s="37"/>
+      <c r="N1" s="37"/>
+      <c r="O1" s="37"/>
+      <c r="P1" s="37"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="D2" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="E2" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="F2" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="G2" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="H2" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="G2" s="11" t="s">
+      <c r="I2" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="H2" s="11" t="s">
+      <c r="J2" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I2" s="11" t="s">
+      <c r="K2" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="J2" s="11" t="s">
+      <c r="L2" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="M2" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="L2" s="11" t="s">
+      <c r="N2" s="11" t="s">
         <v>50</v>
       </c>
-      <c r="M2" s="11" t="s">
+      <c r="O2" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="N2" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="O2" s="11" t="s">
-        <v>53</v>
-      </c>
       <c r="P2" s="13"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="14" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="14"/>
       <c r="C3" s="14"/>
@@ -3337,9 +3298,9 @@
       <c r="O3" s="14"/>
       <c r="P3" s="14"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B4" s="15"/>
       <c r="C4" s="15"/>
@@ -3357,9 +3318,9 @@
       <c r="O4" s="15"/>
       <c r="P4" s="15"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B5" s="15"/>
       <c r="C5" s="15"/>
@@ -3377,9 +3338,9 @@
       <c r="O5" s="15"/>
       <c r="P5" s="15"/>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="15"/>
       <c r="C6" s="15"/>
@@ -3397,9 +3358,9 @@
       <c r="O6" s="15"/>
       <c r="P6" s="15"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B7" s="15"/>
       <c r="C7" s="15"/>
@@ -3417,9 +3378,9 @@
       <c r="O7" s="15"/>
       <c r="P7" s="15"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B8" s="15"/>
       <c r="C8" s="15"/>
@@ -3437,9 +3398,9 @@
       <c r="O8" s="15"/>
       <c r="P8" s="15"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B9" s="15"/>
       <c r="C9" s="15"/>
@@ -3457,9 +3418,9 @@
       <c r="O9" s="15"/>
       <c r="P9" s="15"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
@@ -3477,9 +3438,9 @@
       <c r="O10" s="15"/>
       <c r="P10" s="15"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B11" s="15"/>
       <c r="C11" s="15"/>
@@ -3497,9 +3458,9 @@
       <c r="O11" s="15"/>
       <c r="P11" s="15"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B12" s="15"/>
       <c r="C12" s="15"/>
@@ -3517,9 +3478,9 @@
       <c r="O12" s="15"/>
       <c r="P12" s="15"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B13" s="15"/>
       <c r="C13" s="15"/>
@@ -3537,9 +3498,9 @@
       <c r="O13" s="15"/>
       <c r="P13" s="15"/>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" s="16" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B14" s="16"/>
       <c r="C14" s="16"/>
@@ -3568,100 +3529,102 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:S27"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="16" width="15" customWidth="1"/>
-    <col min="17" max="17" width="20" customWidth="1"/>
-    <col min="18" max="18" width="18" customWidth="1"/>
-    <col min="19" max="19" width="14" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:19" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="41"/>
+      <c r="C1" s="41"/>
+      <c r="D1" s="41"/>
+      <c r="E1" s="41"/>
+      <c r="F1" s="41"/>
+      <c r="G1" s="41"/>
+      <c r="H1" s="41"/>
+      <c r="I1" s="41"/>
+      <c r="J1" s="41"/>
+      <c r="K1" s="41"/>
+      <c r="L1" s="41"/>
+      <c r="M1" s="41"/>
+      <c r="N1" s="41"/>
+      <c r="O1" s="41"/>
+      <c r="P1" s="41"/>
+      <c r="Q1" s="41"/>
+      <c r="R1" s="41"/>
+      <c r="S1" s="41"/>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" s="40" t="s">
+        <v>37</v>
+      </c>
+      <c r="B2" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C2" s="40" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="20"/>
-      <c r="D1" s="20"/>
-      <c r="E1" s="20"/>
-      <c r="F1" s="20"/>
-      <c r="G1" s="20"/>
-      <c r="H1" s="20"/>
-      <c r="I1" s="20"/>
-      <c r="J1" s="20"/>
-      <c r="K1" s="20"/>
-      <c r="L1" s="20"/>
-      <c r="M1" s="20"/>
-      <c r="N1" s="20"/>
-      <c r="O1" s="20"/>
-      <c r="P1" s="20"/>
-      <c r="Q1" s="20"/>
-      <c r="R1" s="20"/>
-      <c r="S1" s="20"/>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
-        <v>39</v>
-      </c>
-      <c r="B2" s="20" t="s">
+      <c r="D2" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="E2" s="40" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="F2" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="G2" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="H2" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="I2" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="J2" s="40" t="s">
         <v>65</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="K2" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="L2" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="M2" s="40" t="s">
         <v>68</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="N2" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="M2" s="20" t="s">
+      <c r="O2" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="P2" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="Q2" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="P2" s="20" t="s">
+      <c r="R2" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="Q2" s="20" t="s">
+      <c r="S2" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="R2" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="S2" s="20" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="20" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="B3" s="20"/>
       <c r="C3" s="20"/>
@@ -3682,9 +3645,9 @@
       <c r="R3" s="20"/>
       <c r="S3" s="20"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A4" s="20" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B4" s="20"/>
       <c r="C4" s="20"/>
@@ -3705,9 +3668,9 @@
       <c r="R4" s="20"/>
       <c r="S4" s="20"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="20" t="s">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="B5" s="20"/>
       <c r="C5" s="20"/>
@@ -3728,9 +3691,9 @@
       <c r="R5" s="20"/>
       <c r="S5" s="20"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B6" s="20"/>
       <c r="C6" s="20"/>
@@ -3751,9 +3714,9 @@
       <c r="R6" s="20"/>
       <c r="S6" s="20"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="20" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B7" s="20"/>
       <c r="C7" s="20"/>
@@ -3774,9 +3737,9 @@
       <c r="R7" s="20"/>
       <c r="S7" s="20"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="B8" s="20"/>
       <c r="C8" s="20"/>
@@ -3797,9 +3760,9 @@
       <c r="R8" s="20"/>
       <c r="S8" s="20"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="20" t="s">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B9" s="20"/>
       <c r="C9" s="20"/>
@@ -3820,9 +3783,9 @@
       <c r="R9" s="20"/>
       <c r="S9" s="20"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="20" t="s">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="B10" s="20"/>
       <c r="C10" s="20"/>
@@ -3843,9 +3806,9 @@
       <c r="R10" s="20"/>
       <c r="S10" s="20"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A11" s="20" t="s">
-        <v>17</v>
+        <v>32</v>
       </c>
       <c r="B11" s="20"/>
       <c r="C11" s="20"/>
@@ -3866,9 +3829,9 @@
       <c r="R11" s="20"/>
       <c r="S11" s="20"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" s="20" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B12" s="20"/>
       <c r="C12" s="20"/>
@@ -3889,9 +3852,9 @@
       <c r="R12" s="20"/>
       <c r="S12" s="20"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="20" t="s">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="B13" s="20"/>
       <c r="C13" s="20"/>
@@ -3912,9 +3875,9 @@
       <c r="R13" s="20"/>
       <c r="S13" s="20"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A14" s="20" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="B14" s="20"/>
       <c r="C14" s="20"/>
@@ -3935,7 +3898,7 @@
       <c r="R14" s="20"/>
       <c r="S14" s="20"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="20"/>
       <c r="B15" s="20"/>
       <c r="C15" s="20"/>
@@ -3956,53 +3919,53 @@
       <c r="R15" s="20"/>
       <c r="S15" s="20"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A16" s="22" t="s">
-        <v>77</v>
-      </c>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="22"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="22"/>
-      <c r="O16" s="22"/>
-      <c r="P16" s="22"/>
-      <c r="Q16" s="22"/>
-      <c r="R16" s="22"/>
-      <c r="S16" s="22"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A17" s="23" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-      <c r="G17" s="23"/>
-      <c r="H17" s="23"/>
-      <c r="I17" s="23"/>
-      <c r="J17" s="23"/>
-      <c r="K17" s="23"/>
-      <c r="L17" s="23"/>
-      <c r="M17" s="23"/>
-      <c r="N17" s="23"/>
-      <c r="O17" s="23"/>
-      <c r="P17" s="23"/>
-      <c r="Q17" s="23"/>
-      <c r="R17" s="23"/>
-      <c r="S17" s="23"/>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="B16" s="21"/>
+      <c r="C16" s="21"/>
+      <c r="D16" s="21"/>
+      <c r="E16" s="21"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="21"/>
+      <c r="R16" s="21"/>
+      <c r="S16" s="21"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A17" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="22"/>
+      <c r="O17" s="22"/>
+      <c r="P17" s="22"/>
+      <c r="Q17" s="22"/>
+      <c r="R17" s="22"/>
+      <c r="S17" s="22"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="20"/>
       <c r="B18" s="20"/>
       <c r="C18" s="20"/>
@@ -4023,32 +3986,32 @@
       <c r="R18" s="20"/>
       <c r="S18" s="20"/>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A19" s="24" t="s">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A19" s="23" t="s">
+        <v>77</v>
+      </c>
+      <c r="B19" s="23"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
+      <c r="I19" s="23"/>
+      <c r="J19" s="23"/>
+      <c r="K19" s="23"/>
+      <c r="L19" s="23"/>
+      <c r="M19" s="23"/>
+      <c r="N19" s="23"/>
+      <c r="O19" s="23"/>
+      <c r="P19" s="23"/>
+      <c r="Q19" s="23"/>
+      <c r="R19" s="23"/>
+      <c r="S19" s="23"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A20" s="20" t="s">
         <v>78</v>
-      </c>
-      <c r="B19" s="24"/>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-      <c r="I19" s="24"/>
-      <c r="J19" s="24"/>
-      <c r="K19" s="24"/>
-      <c r="L19" s="24"/>
-      <c r="M19" s="24"/>
-      <c r="N19" s="24"/>
-      <c r="O19" s="24"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="24"/>
-      <c r="R19" s="24"/>
-      <c r="S19" s="24"/>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A20" s="20" t="s">
-        <v>79</v>
       </c>
       <c r="B20" s="20"/>
       <c r="C20" s="20"/>
@@ -4069,9 +4032,9 @@
       <c r="R20" s="20"/>
       <c r="S20" s="20"/>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A21" s="20" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B21" s="20"/>
       <c r="C21" s="20"/>
@@ -4092,9 +4055,9 @@
       <c r="R21" s="20"/>
       <c r="S21" s="20"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="20" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B22" s="20"/>
       <c r="C22" s="20"/>
@@ -4115,7 +4078,7 @@
       <c r="R22" s="20"/>
       <c r="S22" s="20"/>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="20"/>
       <c r="B23" s="20"/>
       <c r="C23" s="20"/>
@@ -4136,18 +4099,18 @@
       <c r="R23" s="20"/>
       <c r="S23" s="20"/>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.3">
-      <c r="A24" s="24" t="s">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A24" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="23" t="s">
         <v>81</v>
       </c>
-      <c r="B24" s="24" t="s">
+      <c r="C24" s="23" t="s">
+        <v>74</v>
+      </c>
+      <c r="D24" s="23" t="s">
         <v>82</v>
-      </c>
-      <c r="C24" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="D24" s="24" t="s">
-        <v>83</v>
       </c>
       <c r="E24" s="20"/>
       <c r="F24" s="20"/>
@@ -4165,7 +4128,7 @@
       <c r="R24" s="20"/>
       <c r="S24" s="20"/>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="20"/>
       <c r="B25" s="20"/>
       <c r="C25" s="20"/>
@@ -4186,7 +4149,7 @@
       <c r="R25" s="20"/>
       <c r="S25" s="20"/>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="20"/>
       <c r="B26" s="20"/>
       <c r="C26" s="20"/>
@@ -4207,7 +4170,7 @@
       <c r="R26" s="20"/>
       <c r="S26" s="20"/>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="20"/>
       <c r="B27" s="20"/>
       <c r="C27" s="20"/>
@@ -4229,6 +4192,9 @@
       <c r="S27" s="20"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:S1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4236,82 +4202,82 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:B9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="25" t="s">
+    <row r="1" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>83</v>
+      </c>
+      <c r="B1" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="B1" s="26" t="s">
+    </row>
+    <row r="2" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="24" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="25" t="s">
+      <c r="B2" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="B2" s="26" t="s">
+    </row>
+    <row r="3" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="24" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="25" t="s">
+      <c r="B3" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="B3" s="26" t="s">
+    </row>
+    <row r="4" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="24" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="25" t="s">
+      <c r="B4" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="B4" s="26" t="s">
+    </row>
+    <row r="5" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="24" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="25" t="s">
+      <c r="B5" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="B5" s="26" t="s">
+    </row>
+    <row r="6" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="24" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="25" t="s">
+      <c r="B6" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="B6" s="26" t="s">
+    </row>
+    <row r="7" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="24" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="25" t="s">
+      <c r="B7" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="B7" s="26" t="s">
+    </row>
+    <row r="8" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="24" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25" t="s">
+      <c r="B8" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="B8" s="26" t="s">
+    </row>
+    <row r="9" spans="1:2" ht="38.450000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="38.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="27" t="s">
+      <c r="B9" s="27" t="s">
         <v>100</v>
-      </c>
-      <c r="B9" s="28" t="s">
-        <v>101</v>
       </c>
     </row>
   </sheetData>
